--- a/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:54</t>
+          <t>2026-08-24 16:05:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:55</t>
+          <t>2026-08-24 16:05:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:56</t>
+          <t>2026-08-24 16:05:09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:58</t>
+          <t>2026-08-24 16:05:10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:58</t>
+          <t>2026-08-24 16:05:10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:58</t>
+          <t>2026-08-24 16:05:10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:58</t>
+          <t>2026-08-24 16:05:10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 15:04:58</t>
+          <t>2026-08-24 16:05:10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:06</t>
+          <t>2026-08-24 16:42:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:08</t>
+          <t>2026-08-24 16:42:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:09</t>
+          <t>2026-08-24 16:42:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:10</t>
+          <t>2026-08-24 16:42:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:10</t>
+          <t>2026-08-24 16:42:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:10</t>
+          <t>2026-08-24 16:42:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:10</t>
+          <t>2026-08-24 16:42:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:05:10</t>
+          <t>2026-08-24 16:42:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:37</t>
+          <t>2026-08-24 16:56:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:38</t>
+          <t>2026-08-24 16:56:06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:39</t>
+          <t>2026-08-24 16:56:08</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:41</t>
+          <t>2026-08-24 16:56:09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:41</t>
+          <t>2026-08-24 16:56:09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:41</t>
+          <t>2026-08-24 16:56:09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:41</t>
+          <t>2026-08-24 16:56:09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:42:41</t>
+          <t>2026-08-24 16:56:09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17.12%12,000,000</t>
+          <t>17.19%12,000,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.12%</t>
+          <t>17.19%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.68%1,690,000</t>
+          <t>5.53%1,690,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>5.53%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.43%8,460,000</t>
+          <t>5.49%8,460,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.43%</t>
+          <t>5.49%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.09%3,000,000</t>
+          <t>5.17%3,000,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.09%</t>
+          <t>5.17%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.73%2,110,000</t>
+          <t>4.79%2,110,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.79%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.14%60,000,000</t>
+          <t>4.47%60,000,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.47%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.56%1,100,000</t>
+          <t>3.69%1,100,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.69%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.45%1,080,000</t>
+          <t>3.36%1,080,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.21%9,785,000</t>
+          <t>3.25%9,785,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.15%3,040,000</t>
+          <t>3.18%3,040,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.78%2,307,000</t>
+          <t>2.88%2,307,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.78%8,000,000</t>
+          <t>2.86%8,000,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.26%610,000</t>
+          <t>2.32%610,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-4.01%5385</t>
+          <t>-2.1%794</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.01%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5385</v>
+        <v>794</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.08%626,000</t>
+          <t>2.04%4,250,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>626000</v>
+        <v>4250000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:05</t>
+          <t>2026-08-24 19:46:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.1%794</t>
+          <t>-4.01%5385</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>794</v>
+        <v>5385</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.04%4,250,000</t>
+          <t>2.03%626,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>4250000</v>
+        <v>626000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.02%610,000</t>
+          <t>1.97%610,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.77%2,640,000</t>
+          <t>1.81%2,640,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.53%15115</t>
+          <t>+7.33%1010</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>+7.33%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>15115</v>
+        <v>1010</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.63%179,500</t>
+          <t>1.71%2,800,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>179500</v>
+        <v>2800000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-9.89%2050</t>
+          <t>-1.53%15115</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.89%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2050</v>
+        <v>15115</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.62%1,200,000</t>
+          <t>1.64%179,500</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1200000</v>
+        <v>179500</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.61%15,000,000</t>
+          <t>1.60%15,000,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.59%1,800,000</t>
+          <t>1.58%1,800,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+7.33%1010</t>
+          <t>-9.89%2050</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+7.33%</t>
+          <t>-9.89%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1010</v>
+        <v>2050</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.56%2,800,000</t>
+          <t>1.48%1,200,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>2800000</v>
+        <v>1200000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.24%1,000,000</t>
+          <t>1.25%1,000,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.03%1,600,000</t>
+          <t>1.10%1,600,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.02%9,000,000</t>
+          <t>0.98%9,000,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.85%5,360,000</t>
+          <t>0.87%5,360,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.73%700,000</t>
+          <t>0.72%700,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.72%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.59%1,800,000</t>
+          <t>0.55%1,800,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.50%525,000</t>
+          <t>0.51%525,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:06</t>
+          <t>2026-08-24 19:46:40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.46%3,200,000</t>
+          <t>0.47%3,200,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.41%2,000,000</t>
+          <t>0.39%2,000,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.33%4,500,000</t>
+          <t>0.34%4,500,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.36%417</t>
+          <t>+7.66%14410</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>+7.66%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>417</v>
+        <v>14410</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.21%800,000</t>
+          <t>0.30%35,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>800000</v>
+        <v>35000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4966譜瑞-KY</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.59%557</t>
+          <t>-4.36%417</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.59%</t>
+          <t>-4.36%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>557</v>
+        <v>417</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.17%500,000</t>
+          <t>0.20%800,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>4966譜瑞-KY</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.15%680</t>
+          <t>-1.59%557</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>680</v>
+        <v>557</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.16%393,000</t>
+          <t>0.17%500,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>393000</v>
+        <v>500000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+7.66%14410</t>
+          <t>+0.15%680</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>14410</v>
+        <v>680</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.16%20,000</t>
+          <t>0.16%393,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,11 +2849,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>20000</v>
+        <v>393000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.08%700,000</t>
+          <t>0.09%700,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:08</t>
+          <t>2026-08-24 19:46:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:09</t>
+          <t>2026-08-24 19:46:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:09</t>
+          <t>2026-08-24 19:46:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:09</t>
+          <t>2026-08-24 19:46:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:09</t>
+          <t>2026-08-24 19:46:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 16:56:09</t>
+          <t>2026-08-24 19:46:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:39</t>
+          <t>2026-08-24 19:59:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:40</t>
+          <t>2026-08-24 19:59:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:42</t>
+          <t>2026-08-24 19:59:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:43</t>
+          <t>2026-08-24 19:59:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:43</t>
+          <t>2026-08-24 19:59:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:43</t>
+          <t>2026-08-24 19:59:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:43</t>
+          <t>2026-08-24 19:59:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 19:46:43</t>
+          <t>2026-08-24 19:59:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:20</t>
+          <t>2026-08-24 20:04:35</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:21</t>
+          <t>2026-08-24 20:04:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:23</t>
+          <t>2026-08-24 20:04:38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:24</t>
+          <t>2026-08-24 20:04:39</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:24</t>
+          <t>2026-08-24 20:04:39</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:24</t>
+          <t>2026-08-24 20:04:39</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:24</t>
+          <t>2026-08-24 20:04:39</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 19:59:24</t>
+          <t>2026-08-24 20:04:39</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-24_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:35</t>
+          <t>2026-08-24 23:03:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:36</t>
+          <t>2026-08-24 23:03:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:38</t>
+          <t>2026-08-24 23:04:01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:39</t>
+          <t>2026-08-24 23:04:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:39</t>
+          <t>2026-08-24 23:04:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:39</t>
+          <t>2026-08-24 23:04:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:39</t>
+          <t>2026-08-24 23:04:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-24 20:04:39</t>
+          <t>2026-08-24 23:04:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
